--- a/spt/spt_processing_input_2.xlsx
+++ b/spt/spt_processing_input_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eafit-my.sharepoint.com/personal/eamontoyaa_eafit_edu_co/Documents/EAMA/Dev/GitHub/data4testing/spt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eiaedu-my.sharepoint.com/personal/exneyder_montoya_eia_edu_co/Documents/EAMA/Dev/data4testing/spt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{4B994FE8-3705-4D8C-BF12-07F72C073787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{423E2B5E-3D49-4566-BDFE-098D095068D6}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{4B994FE8-3705-4D8C-BF12-07F72C073787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CAF6FDC-EFCF-404A-873A-7E0FC388CF5B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7008F4F0-F30C-4941-AFE3-8359CC08712A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7008F4F0-F30C-4941-AFE3-8359CC08712A}"/>
   </bookViews>
   <sheets>
     <sheet name="inputs" sheetId="1" r:id="rId1"/>
@@ -41,15 +41,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="14">
   <si>
     <t>Material</t>
   </si>
   <si>
     <t>Profundidad_(m)</t>
-  </si>
-  <si>
-    <t>Revestimiento_(m)</t>
   </si>
   <si>
     <t>Descripción</t>
@@ -484,318 +481,269 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97243F2A-F833-4870-8595-53EB31C9E5F3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1">
         <v>0.25</v>
       </c>
       <c r="D2" s="1">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>1.25</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1">
         <v>2.25</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1">
         <v>4.25</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1">
         <v>5.25</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1">
         <v>7.25</v>
       </c>
       <c r="D7" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1">
         <v>8.25</v>
       </c>
       <c r="D8" s="1">
-        <v>6</v>
-      </c>
-      <c r="E8" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1">
         <v>10.25</v>
       </c>
       <c r="D9" s="1">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1">
-        <v>19</v>
-      </c>
-      <c r="F9" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1">
         <v>11.25</v>
       </c>
       <c r="D10" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E10" s="1">
-        <v>16</v>
-      </c>
-      <c r="F10" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1">
         <v>12.25</v>
       </c>
       <c r="D11" s="1">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1">
-        <v>33</v>
-      </c>
-      <c r="F11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="1">
         <v>13.25</v>
       </c>
       <c r="D12" s="1">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E12" s="1">
-        <v>42</v>
-      </c>
-      <c r="F12" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1">
         <v>14.25</v>
       </c>
       <c r="D13" s="1">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1">
-        <v>60</v>
-      </c>
-      <c r="F13" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1">
         <v>15.25</v>
       </c>
       <c r="D14" s="1">
-        <v>6</v>
-      </c>
-      <c r="E14" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1">
         <v>16.25</v>
       </c>
       <c r="D15" s="1">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E15" s="1">
-        <v>33</v>
-      </c>
-      <c r="F15" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1">
         <v>17.25</v>
       </c>
       <c r="D16" s="1">
-        <v>6</v>
-      </c>
-      <c r="E16" s="1">
         <v>63</v>
       </c>
     </row>
@@ -829,41 +777,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a21f4c27-33e5-4cad-a1ff-6167bd9f9a45}" enabled="0" method="" siteId="{a21f4c27-33e5-4cad-a1ff-6167bd9f9a45}" removed="1"/>
+</clbl:labelList>
 </file>